--- a/output/modeling/model_performance.xlsx
+++ b/output/modeling/model_performance.xlsx
@@ -1,38 +1,163 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="folds" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="summary" sheetId="1" r:id="rId1"/>
+    <sheet name="folds" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="39">
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>AUC mean</t>
+  </si>
+  <si>
+    <t>AUC sd</t>
+  </si>
+  <si>
+    <t>Average precision mean</t>
+  </si>
+  <si>
+    <t>Average precision sd</t>
+  </si>
+  <si>
+    <t>Accuracy mean</t>
+  </si>
+  <si>
+    <t>Accuracy sd</t>
+  </si>
+  <si>
+    <t>Sensitivity mean</t>
+  </si>
+  <si>
+    <t>Sensitivity sd</t>
+  </si>
+  <si>
+    <t>Specificity mean</t>
+  </si>
+  <si>
+    <t>Specificity sd</t>
+  </si>
+  <si>
+    <t>Precision mean</t>
+  </si>
+  <si>
+    <t>Precision sd</t>
+  </si>
+  <si>
+    <t>F1 mean</t>
+  </si>
+  <si>
+    <t>F1 sd</t>
+  </si>
+  <si>
+    <t>Brier score mean</t>
+  </si>
+  <si>
+    <t>Brier score sd</t>
+  </si>
+  <si>
+    <t>OOF AUC</t>
+  </si>
+  <si>
+    <t>OOF average precision</t>
+  </si>
+  <si>
+    <t>OOF Brier score</t>
+  </si>
+  <si>
+    <t>OOF TN</t>
+  </si>
+  <si>
+    <t>OOF FP</t>
+  </si>
+  <si>
+    <t>OOF FN</t>
+  </si>
+  <si>
+    <t>OOF TP</t>
+  </si>
+  <si>
+    <t>Random Forest</t>
+  </si>
+  <si>
+    <t>Gradient Boosting</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>SVM</t>
+  </si>
+  <si>
+    <t>Gaussian NB</t>
+  </si>
+  <si>
+    <t>Logistic Regression</t>
+  </si>
+  <si>
+    <t>fold</t>
+  </si>
+  <si>
+    <t>AUC</t>
+  </si>
+  <si>
+    <t>Average precision</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Sensitivity</t>
+  </si>
+  <si>
+    <t>Specificity</t>
+  </si>
+  <si>
+    <t>Precision</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Brier score</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,93 +172,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -421,1679 +488,1531 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:X7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>AUC mean</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>AUC sd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Average precision mean</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Average precision sd</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy mean</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy sd</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sensitivity mean</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Sensitivity sd</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Specificity mean</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Specificity sd</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Precision mean</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Precision sd</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>F1 mean</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>F1 sd</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Brier score mean</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Brier score sd</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>OOF AUC</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>OOF average precision</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>OOF Brier score</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>OOF TN</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>OOF FP</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>OOF FN</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>OOF TP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:24">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2">
         <v>0.9215257531584061</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0.04077741427570997</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.845350275324353</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.05982472618660738</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.8939580133128521</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.02657297153176835</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0.7142857142857142</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>0.1336306209562122</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0.9460884353741497</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>0.01119013372302301</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>0.7930128205128206</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0.03342904159301827</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>0.7471225071225071</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>0.07793926235113571</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>0.08816921932186206</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0.01045912162112869</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="Q2">
+        <v>0.01045912162112868</v>
+      </c>
+      <c r="R2">
         <v>0.9167160640189685</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2">
         <v>0.8423597225847882</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2">
         <v>0.08820965487014941</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2">
         <v>228</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2">
         <v>13</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W2">
         <v>20</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X2">
         <v>50</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Gradient Boosting</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:24">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3">
         <v>0.8989522594752186</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0.04011187464445189</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.8302993123646717</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.04215137621583544</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.9004096262160779</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.02595190500555084</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0.7285714285714285</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>0.07824607964359513</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>0.9503401360544217</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>0.04287835393202748</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>0.8294881588999237</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>0.1265787478662408</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>0.7683625192012288</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>0.05128199458632479</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>0.08134831491004504</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>0.02019459952499365</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3">
         <v>0.8945465323058684</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3">
         <v>0.8269547776066588</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3">
         <v>0.08144616718683408</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3">
         <v>229</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3">
         <v>12</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W3">
         <v>19</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X3">
         <v>51</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:24">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4">
         <v>0.8886965500485908</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0.05560925598324203</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.7990142675621082</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.08019996106957759</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.8908346134152586</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.02770754995161028</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0.7571428571428571</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>0.1083267920578793</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>0.9295918367346939</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>0.03104411212807274</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>0.7634920634920636</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>0.08140242161878149</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>0.7559065934065934</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>0.06562499101500216</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>0.09140208431628424</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>0.01649452324920299</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4">
         <v>0.889330171902786</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4">
         <v>0.7993158310077941</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4">
         <v>0.09149040673111851</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4">
         <v>224</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4">
         <v>17</v>
       </c>
-      <c r="W4" t="n">
+      <c r="W4">
         <v>17</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X4">
         <v>53</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:24">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5">
         <v>0.8553996598639456</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.06019505810292742</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.7952020108942011</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.07686890301544881</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.8971326164874552</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.02916250266209029</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>0.6571428571428573</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>0.09313146293146642</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>0.966921768707483</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>0.02762198752407132</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>0.8606643356643356</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>0.1031646304462377</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>0.7405490805490805</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>0.07956947348307573</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>0.08867252111981734</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>0.01986297918699684</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5">
         <v>0.8564908120924719</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5">
         <v>0.7990972811931079</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5">
         <v>0.08867729298871248</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5">
         <v>233</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5">
         <v>8</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W5">
         <v>24</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X5">
         <v>46</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Gaussian NB</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:24">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6">
         <v>0.8569302721088435</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0.06537547159746271</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.728578403993143</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.04498953094459637</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.5109062980030722</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>0.146985024545972</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>0.9</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>0.06388765649999402</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>0.3977891156462585</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>0.1785505737741183</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>0.3122130798874985</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>0.0649151441529103</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>0.4616973123345448</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>0.08019052505719675</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>0.4590585176943037</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>0.1524192575971076</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6">
         <v>0.8528156490812092</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6">
         <v>0.7157284795749408</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6">
         <v>0.4586957091699086</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U6">
         <v>96</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6">
         <v>145</v>
       </c>
-      <c r="W6" t="n">
+      <c r="W6">
         <v>7</v>
       </c>
-      <c r="X6" t="n">
+      <c r="X6">
         <v>63</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:24">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7">
         <v>0.8483661321671526</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.04761788551466705</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.8184239307267724</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.04892056143049755</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.8649257552483359</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>0.03544213755164115</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>0.7428571428571428</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>0.06388765649999396</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>0.9004251700680271</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>0.03084373687103363</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>0.6875</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>0.08060477716637406</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>0.7133333333333333</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>0.06871017708734384</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>0.1099854403337434</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>0.01528182621833185</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7">
         <v>0.8487255483106104</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7">
         <v>0.8172910647252214</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7">
         <v>0.1099657010921379</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U7">
         <v>217</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7">
         <v>24</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W7">
         <v>18</v>
       </c>
-      <c r="X7" t="n">
+      <c r="X7">
         <v>52</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>fold</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Average precision</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Sensitivity</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Specificity</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Brier score</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0.8921282798833819</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.8503360674413305</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.873015873015873</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.7857142857142857</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.8979591836734694</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0.6875</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>0.7333333333333333</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0.1038465361944411</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0.8229166666666667</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.7561974355876483</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.8064516129032258</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.6428571428571429</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.8541666666666666</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0.5625</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>0.6</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>0.1370967331457805</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0.7946428571428571</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.7918909840358908</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.8709677419354839</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.9166666666666666</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0.7142857142857143</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>0.7142857142857143</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>0.1061371209336563</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.9047619047619049</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.8812173290368777</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.8709677419354839</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.7857142857142857</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.8958333333333334</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>0.6875</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>0.7333333333333333</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>0.1013912197896277</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0.8273809523809523</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.8124778375321144</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.9032258064516129</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.7857142857142857</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>0.9375</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>0.7857142857142857</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>0.7857142857142857</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>0.1014555916052116</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.9052478134110787</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.7574778396206967</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.873015873015873</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.6428571428571429</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>0.9387755102040817</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>0.75</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>0.6923076923076923</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>0.1007446748392219</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>0.9464285714285714</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>0.8917768720391381</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.8870967741935484</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>0.9375</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>0.7692307692307693</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>0.7407407407407407</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>0.08058740787094229</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
         <v>3</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>0.8645833333333334</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>0.8201386682221921</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0.9032258064516129</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>0.9583333333333334</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>0.8333333333333334</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>0.7692307692307693</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>0.0925464678750603</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
         <v>4</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>0.9717261904761905</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>0.9068016309087736</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0.9354838709677419</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>0.9285714285714286</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>0.9375</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>0.8125</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>0.8666666666666667</v>
       </c>
-      <c r="J10" t="n">
-        <v>0.07457086566216599</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+      <c r="J10">
+        <v>0.074570865662166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11">
         <v>5</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>0.9196428571428572</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0.8505563658309652</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0.8709677419354839</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>0.5714285714285714</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>0.9583333333333334</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>0.8</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>0.6666666666666666</v>
       </c>
-      <c r="J11" t="n">
-        <v>0.09239668036191986</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Gradient Boosting</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+      <c r="J11">
+        <v>0.09239668036191985</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>0.8943148688046647</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>0.7789523180586577</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.873015873015873</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>0.9183673469387755</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>0.7142857142857143</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>0.7142857142857143</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>0.111780372991433</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Gradient Boosting</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>0.9270833333333333</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>0.8941249226963512</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>0.9354838709677419</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>0.8333333333333334</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>0.05800350672184984</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Gradient Boosting</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>3</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>0.8675595238095237</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>0.8376259540728536</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>0.9193548387096774</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>0.9791666666666666</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>0.9090909090909091</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>0.8</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>0.06952445403499236</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Gradient Boosting</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>0.9508928571428572</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>0.8289677952520721</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>0.8870967741935484</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>0.8571428571428571</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>0.8958333333333334</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>0.7058823529411765</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>0.7741935483870968</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>0.08157468859795679</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Gradient Boosting</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
         <v>5</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>0.8549107142857143</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>0.8118255717434238</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>0.8870967741935484</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>0.6428571428571429</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>0.9583333333333334</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>0.8181818181818182</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>0.72</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>0.08585855220399326</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>0.846938775510204</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>0.7856715928720536</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>0.8888888888888888</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>0.9387755102040817</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>0.7692307692307693</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>0.7407407407407407</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>0.09015657234620711</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
         <v>2</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>0.8184523809523809</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>0.7179811611839261</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>0.8709677419354839</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>0.5</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>0.9791666666666666</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>0.875</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>0.6363636363636364</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>0.110128169182962</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19">
         <v>3</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>0.806547619047619</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>0.7982024867363212</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>0.9193548387096774</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>0.9791666666666666</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>0.9090909090909091</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>0.8</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>0.08305765497542665</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20">
         <v>4</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>0.9583333333333333</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>0.9209383753501399</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>0.9354838709677419</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>1</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>0.8333333333333334</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>0.05839988840641006</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21">
         <v>5</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>0.8467261904761905</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>0.7532164383285646</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>0.8709677419354839</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>0.6428571428571429</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>0.9375</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>0.75</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>0.6923076923076923</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>0.1016203206880809</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Gaussian NB</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>0.8724489795918366</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>0.742320915131975</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>0.6190476190476191</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>0.9285714285714286</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>0.5306122448979592</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>0.3611111111111111</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>0.52</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>0.3462250666074355</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Gaussian NB</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23">
         <v>2</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>0.8601190476190476</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>0.7493074490254942</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>0.5645161290322581</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>0.8571428571428571</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>0.4791666666666667</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>0.3243243243243243</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>0.4705882352941176</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>0.4027168712684491</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Gaussian NB</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24">
         <v>3</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>0.8035714285714286</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>0.6592996503812443</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>0.2741935483870968</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>0.8571428571428571</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>0.1041666666666667</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>0.2181818181818182</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>0.3478260869565217</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>0.7127136912519318</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Gaussian NB</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25">
         <v>4</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>0.9561011904761905</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>0.778171795033803</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>0.6290322580645161</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>1</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>0.5208333333333334</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>0.3783783783783784</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>0.5490196078431373</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>0.3493226914964466</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Gaussian NB</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26">
         <v>5</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>0.7924107142857143</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>0.7137922103931988</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>0.4677419354838709</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>0.8571428571428571</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>0.3541666666666667</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>0.2790697674418605</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>0.4210526315789473</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>0.4843142678472553</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>0.8556851311953353</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>0.6721541950113379</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>0.8412698412698413</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>0.6428571428571429</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>0.8979591836734694</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>0.6428571428571429</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>0.6428571428571429</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>0.1188703553297385</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28">
         <v>2</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>0.9375</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>0.8813675470188074</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>0.9032258064516129</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>0.7857142857142857</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>0.9375</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>0.7857142857142857</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>0.7857142857142857</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>0.07991783895889881</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29">
         <v>3</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>0.8601190476190477</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>0.800519535737731</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>0.9032258064516129</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>0.9583333333333334</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>0.8333333333333334</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>0.7692307692307693</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>0.08945656492932137</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30">
         <v>4</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>0.9583333333333334</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>0.8515453617344372</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>0.9032258064516129</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>0.9285714285714286</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>0.8958333333333334</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>0.7222222222222222</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>0.8125</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>0.07732738965912343</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31">
         <v>5</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>0.831845238095238</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>0.7894846983082277</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>0.9032258064516129</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>0.9583333333333334</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>0.8333333333333334</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>0.7692307692307693</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>0.09143827270433903</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/output/modeling/model_performance.xlsx
+++ b/output/modeling/model_performance.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="43">
   <si>
     <t>model</t>
   </si>
@@ -92,10 +92,22 @@
     <t>Random Forest</t>
   </si>
   <si>
+    <t>Weighted Soft Voting Ensemble</t>
+  </si>
+  <si>
+    <t>Stacking Ensemble</t>
+  </si>
+  <si>
+    <t>Soft Voting Ensemble</t>
+  </si>
+  <si>
     <t>Gradient Boosting</t>
   </si>
   <si>
     <t>XGBoost</t>
+  </si>
+  <si>
+    <t>Hard Voting Ensemble</t>
   </si>
   <si>
     <t>SVM</t>
@@ -489,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
@@ -645,61 +657,61 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>0.8989522594752186</v>
+        <v>0.9194484936831875</v>
       </c>
       <c r="C3">
-        <v>0.04011187464445189</v>
+        <v>0.04693638752251705</v>
       </c>
       <c r="D3">
-        <v>0.8302993123646717</v>
+        <v>0.8550589280551095</v>
       </c>
       <c r="E3">
-        <v>0.04215137621583544</v>
+        <v>0.06150620756041383</v>
       </c>
       <c r="F3">
         <v>0.9004096262160779</v>
       </c>
       <c r="G3">
-        <v>0.02595190500555084</v>
+        <v>0.02331155362961233</v>
       </c>
       <c r="H3">
         <v>0.7285714285714285</v>
       </c>
       <c r="I3">
-        <v>0.07824607964359513</v>
+        <v>0.1173691194653927</v>
       </c>
       <c r="J3">
-        <v>0.9503401360544217</v>
+        <v>0.9502551020408163</v>
       </c>
       <c r="K3">
-        <v>0.04287835393202748</v>
+        <v>0.01107076238630234</v>
       </c>
       <c r="L3">
-        <v>0.8294881588999237</v>
+        <v>0.8094696969696971</v>
       </c>
       <c r="M3">
-        <v>0.1265787478662408</v>
+        <v>0.03449882219413251</v>
       </c>
       <c r="N3">
-        <v>0.7683625192012288</v>
+        <v>0.7634871794871796</v>
       </c>
       <c r="O3">
-        <v>0.05128199458632479</v>
+        <v>0.0664635960428569</v>
       </c>
       <c r="P3">
-        <v>0.08134831491004504</v>
+        <v>0.08333353663299525</v>
       </c>
       <c r="Q3">
-        <v>0.02019459952499365</v>
+        <v>0.01069150387203927</v>
       </c>
       <c r="R3">
-        <v>0.8945465323058684</v>
+        <v>0.9148784825133374</v>
       </c>
       <c r="S3">
-        <v>0.8269547776066588</v>
+        <v>0.8516515486301728</v>
       </c>
       <c r="T3">
-        <v>0.08144616718683408</v>
+        <v>0.08337667493737058</v>
       </c>
       <c r="U3">
         <v>229</v>
@@ -719,73 +731,73 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>0.8886965500485908</v>
+        <v>0.9025510204081633</v>
       </c>
       <c r="C4">
-        <v>0.05560925598324203</v>
+        <v>0.04426661588432256</v>
       </c>
       <c r="D4">
-        <v>0.7990142675621082</v>
+        <v>0.8329691304798326</v>
       </c>
       <c r="E4">
-        <v>0.08019996106957759</v>
+        <v>0.04103037370965597</v>
       </c>
       <c r="F4">
-        <v>0.8908346134152586</v>
+        <v>0.8844342037890425</v>
       </c>
       <c r="G4">
-        <v>0.02770754995161028</v>
+        <v>0.03560956923227209</v>
       </c>
       <c r="H4">
-        <v>0.7571428571428571</v>
+        <v>0.7857142857142858</v>
       </c>
       <c r="I4">
-        <v>0.1083267920578793</v>
+        <v>0.1237179148263484</v>
       </c>
       <c r="J4">
-        <v>0.9295918367346939</v>
+        <v>0.9130952380952382</v>
       </c>
       <c r="K4">
-        <v>0.03104411212807274</v>
+        <v>0.03610893068595978</v>
       </c>
       <c r="L4">
-        <v>0.7634920634920636</v>
+        <v>0.7298506447113258</v>
       </c>
       <c r="M4">
-        <v>0.08140242161878149</v>
+        <v>0.0811266337968914</v>
       </c>
       <c r="N4">
-        <v>0.7559065934065934</v>
+        <v>0.7521683812006392</v>
       </c>
       <c r="O4">
-        <v>0.06562499101500216</v>
+        <v>0.07435369696742616</v>
       </c>
       <c r="P4">
-        <v>0.09140208431628424</v>
+        <v>0.1063901896788903</v>
       </c>
       <c r="Q4">
-        <v>0.01649452324920299</v>
+        <v>0.01360300645005625</v>
       </c>
       <c r="R4">
-        <v>0.889330171902786</v>
+        <v>0.9039122703023118</v>
       </c>
       <c r="S4">
-        <v>0.7993158310077941</v>
+        <v>0.8402477430016286</v>
       </c>
       <c r="T4">
-        <v>0.09149040673111851</v>
+        <v>0.1064675690831278</v>
       </c>
       <c r="U4">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="V4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="W4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="X4">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -793,73 +805,73 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>0.8553996598639456</v>
+        <v>0.8984390184645287</v>
       </c>
       <c r="C5">
-        <v>0.06019505810292742</v>
+        <v>0.05618710834558166</v>
       </c>
       <c r="D5">
-        <v>0.7952020108942011</v>
+        <v>0.8433989836973563</v>
       </c>
       <c r="E5">
-        <v>0.07686890301544881</v>
+        <v>0.06342221083432939</v>
       </c>
       <c r="F5">
-        <v>0.8971326164874552</v>
+        <v>0.8971838197644649</v>
       </c>
       <c r="G5">
-        <v>0.02916250266209029</v>
+        <v>0.0176805219501351</v>
       </c>
       <c r="H5">
-        <v>0.6571428571428573</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I5">
-        <v>0.09313146293146642</v>
+        <v>0.05050762722761051</v>
       </c>
       <c r="J5">
-        <v>0.966921768707483</v>
+        <v>0.9503401360544217</v>
       </c>
       <c r="K5">
-        <v>0.02762198752407132</v>
+        <v>0.02316181993252872</v>
       </c>
       <c r="L5">
-        <v>0.8606643356643356</v>
+        <v>0.8121212121212121</v>
       </c>
       <c r="M5">
-        <v>0.1031646304462377</v>
+        <v>0.07099105148100526</v>
       </c>
       <c r="N5">
-        <v>0.7405490805490805</v>
+        <v>0.7578461538461537</v>
       </c>
       <c r="O5">
-        <v>0.07956947348307573</v>
+        <v>0.0387718720288394</v>
       </c>
       <c r="P5">
-        <v>0.08867252111981734</v>
+        <v>0.080125096472959</v>
       </c>
       <c r="Q5">
-        <v>0.01986297918699684</v>
+        <v>0.01159455341001293</v>
       </c>
       <c r="R5">
-        <v>0.8564908120924719</v>
+        <v>0.8969768820391226</v>
       </c>
       <c r="S5">
-        <v>0.7990972811931079</v>
+        <v>0.8423243719943517</v>
       </c>
       <c r="T5">
-        <v>0.08867729298871248</v>
+        <v>0.08017308181375768</v>
       </c>
       <c r="U5">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="W5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="X5">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -867,73 +879,73 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>0.8569302721088435</v>
+        <v>0.8989522594752186</v>
       </c>
       <c r="C6">
-        <v>0.06537547159746271</v>
+        <v>0.04011187464445189</v>
       </c>
       <c r="D6">
-        <v>0.728578403993143</v>
+        <v>0.8302993123646717</v>
       </c>
       <c r="E6">
-        <v>0.04498953094459637</v>
+        <v>0.04215137621583544</v>
       </c>
       <c r="F6">
-        <v>0.5109062980030722</v>
+        <v>0.9004096262160779</v>
       </c>
       <c r="G6">
-        <v>0.146985024545972</v>
+        <v>0.02595190500555084</v>
       </c>
       <c r="H6">
-        <v>0.9</v>
+        <v>0.7285714285714285</v>
       </c>
       <c r="I6">
-        <v>0.06388765649999402</v>
+        <v>0.07824607964359513</v>
       </c>
       <c r="J6">
-        <v>0.3977891156462585</v>
+        <v>0.9503401360544217</v>
       </c>
       <c r="K6">
-        <v>0.1785505737741183</v>
+        <v>0.04287835393202748</v>
       </c>
       <c r="L6">
-        <v>0.3122130798874985</v>
+        <v>0.8294881588999237</v>
       </c>
       <c r="M6">
-        <v>0.0649151441529103</v>
+        <v>0.1265787478662408</v>
       </c>
       <c r="N6">
-        <v>0.4616973123345448</v>
+        <v>0.7683625192012288</v>
       </c>
       <c r="O6">
-        <v>0.08019052505719675</v>
+        <v>0.05128199458632479</v>
       </c>
       <c r="P6">
-        <v>0.4590585176943037</v>
+        <v>0.08134831491004504</v>
       </c>
       <c r="Q6">
-        <v>0.1524192575971076</v>
+        <v>0.02019459952499365</v>
       </c>
       <c r="R6">
-        <v>0.8528156490812092</v>
+        <v>0.8945465323058684</v>
       </c>
       <c r="S6">
-        <v>0.7157284795749408</v>
+        <v>0.8269547776066588</v>
       </c>
       <c r="T6">
-        <v>0.4586957091699086</v>
+        <v>0.08144616718683408</v>
       </c>
       <c r="U6">
-        <v>96</v>
+        <v>229</v>
       </c>
       <c r="V6">
-        <v>145</v>
+        <v>12</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="X6">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -941,72 +953,368 @@
         <v>29</v>
       </c>
       <c r="B7">
+        <v>0.8886965500485908</v>
+      </c>
+      <c r="C7">
+        <v>0.05560925598324203</v>
+      </c>
+      <c r="D7">
+        <v>0.7990142675621082</v>
+      </c>
+      <c r="E7">
+        <v>0.08019996106957759</v>
+      </c>
+      <c r="F7">
+        <v>0.8908346134152586</v>
+      </c>
+      <c r="G7">
+        <v>0.02770754995161028</v>
+      </c>
+      <c r="H7">
+        <v>0.7571428571428571</v>
+      </c>
+      <c r="I7">
+        <v>0.1083267920578793</v>
+      </c>
+      <c r="J7">
+        <v>0.9295918367346939</v>
+      </c>
+      <c r="K7">
+        <v>0.03104411212807274</v>
+      </c>
+      <c r="L7">
+        <v>0.7634920634920636</v>
+      </c>
+      <c r="M7">
+        <v>0.08140242161878149</v>
+      </c>
+      <c r="N7">
+        <v>0.7559065934065934</v>
+      </c>
+      <c r="O7">
+        <v>0.06562499101500216</v>
+      </c>
+      <c r="P7">
+        <v>0.09140208431628424</v>
+      </c>
+      <c r="Q7">
+        <v>0.01649452324920299</v>
+      </c>
+      <c r="R7">
+        <v>0.889330171902786</v>
+      </c>
+      <c r="S7">
+        <v>0.7993158310077941</v>
+      </c>
+      <c r="T7">
+        <v>0.09149040673111851</v>
+      </c>
+      <c r="U7">
+        <v>224</v>
+      </c>
+      <c r="V7">
+        <v>17</v>
+      </c>
+      <c r="W7">
+        <v>17</v>
+      </c>
+      <c r="X7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8">
+        <v>0.8765245383867832</v>
+      </c>
+      <c r="C8">
+        <v>0.05385670844614063</v>
+      </c>
+      <c r="D8">
+        <v>0.7507026055640535</v>
+      </c>
+      <c r="E8">
+        <v>0.07759891072161156</v>
+      </c>
+      <c r="F8">
+        <v>0.9035842293906811</v>
+      </c>
+      <c r="G8">
+        <v>0.01078251538099737</v>
+      </c>
+      <c r="H8">
+        <v>0.7285714285714285</v>
+      </c>
+      <c r="I8">
+        <v>0.03194382824999698</v>
+      </c>
+      <c r="J8">
+        <v>0.9544217687074831</v>
+      </c>
+      <c r="K8">
+        <v>0.0171322963434534</v>
+      </c>
+      <c r="L8">
+        <v>0.8261405261405261</v>
+      </c>
+      <c r="M8">
+        <v>0.0544454780692777</v>
+      </c>
+      <c r="N8">
+        <v>0.772983312983313</v>
+      </c>
+      <c r="O8">
+        <v>0.02213439449183894</v>
+      </c>
+      <c r="P8">
+        <v>0.08558320532514081</v>
+      </c>
+      <c r="Q8">
+        <v>0.01716329934848846</v>
+      </c>
+      <c r="R8">
+        <v>0.8772080616478957</v>
+      </c>
+      <c r="S8">
+        <v>0.7498332211303969</v>
+      </c>
+      <c r="T8">
+        <v>0.08565916398713827</v>
+      </c>
+      <c r="U8">
+        <v>230</v>
+      </c>
+      <c r="V8">
+        <v>11</v>
+      </c>
+      <c r="W8">
+        <v>19</v>
+      </c>
+      <c r="X8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9">
+        <v>0.8553996598639456</v>
+      </c>
+      <c r="C9">
+        <v>0.06019505810292742</v>
+      </c>
+      <c r="D9">
+        <v>0.7952020108942011</v>
+      </c>
+      <c r="E9">
+        <v>0.07686890301544881</v>
+      </c>
+      <c r="F9">
+        <v>0.8971326164874552</v>
+      </c>
+      <c r="G9">
+        <v>0.02916250266209029</v>
+      </c>
+      <c r="H9">
+        <v>0.6571428571428573</v>
+      </c>
+      <c r="I9">
+        <v>0.09313146293146642</v>
+      </c>
+      <c r="J9">
+        <v>0.966921768707483</v>
+      </c>
+      <c r="K9">
+        <v>0.02762198752407132</v>
+      </c>
+      <c r="L9">
+        <v>0.8606643356643356</v>
+      </c>
+      <c r="M9">
+        <v>0.1031646304462377</v>
+      </c>
+      <c r="N9">
+        <v>0.7405490805490805</v>
+      </c>
+      <c r="O9">
+        <v>0.07956947348307573</v>
+      </c>
+      <c r="P9">
+        <v>0.08867252111981734</v>
+      </c>
+      <c r="Q9">
+        <v>0.01986297918699684</v>
+      </c>
+      <c r="R9">
+        <v>0.8564908120924719</v>
+      </c>
+      <c r="S9">
+        <v>0.7990972811931079</v>
+      </c>
+      <c r="T9">
+        <v>0.08867729298871248</v>
+      </c>
+      <c r="U9">
+        <v>233</v>
+      </c>
+      <c r="V9">
+        <v>8</v>
+      </c>
+      <c r="W9">
+        <v>24</v>
+      </c>
+      <c r="X9">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>0.8569302721088435</v>
+      </c>
+      <c r="C10">
+        <v>0.06537547159746271</v>
+      </c>
+      <c r="D10">
+        <v>0.728578403993143</v>
+      </c>
+      <c r="E10">
+        <v>0.04498953094459637</v>
+      </c>
+      <c r="F10">
+        <v>0.5109062980030722</v>
+      </c>
+      <c r="G10">
+        <v>0.146985024545972</v>
+      </c>
+      <c r="H10">
+        <v>0.9</v>
+      </c>
+      <c r="I10">
+        <v>0.06388765649999402</v>
+      </c>
+      <c r="J10">
+        <v>0.3977891156462585</v>
+      </c>
+      <c r="K10">
+        <v>0.1785505737741183</v>
+      </c>
+      <c r="L10">
+        <v>0.3122130798874985</v>
+      </c>
+      <c r="M10">
+        <v>0.0649151441529103</v>
+      </c>
+      <c r="N10">
+        <v>0.4616973123345448</v>
+      </c>
+      <c r="O10">
+        <v>0.08019052505719675</v>
+      </c>
+      <c r="P10">
+        <v>0.4590585176943037</v>
+      </c>
+      <c r="Q10">
+        <v>0.1524192575971076</v>
+      </c>
+      <c r="R10">
+        <v>0.8528156490812092</v>
+      </c>
+      <c r="S10">
+        <v>0.7157284795749408</v>
+      </c>
+      <c r="T10">
+        <v>0.4586957091699086</v>
+      </c>
+      <c r="U10">
+        <v>96</v>
+      </c>
+      <c r="V10">
+        <v>145</v>
+      </c>
+      <c r="W10">
+        <v>7</v>
+      </c>
+      <c r="X10">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
         <v>0.8483661321671526</v>
       </c>
-      <c r="C7">
+      <c r="C11">
         <v>0.04761788551466705</v>
       </c>
-      <c r="D7">
+      <c r="D11">
         <v>0.8184239307267724</v>
       </c>
-      <c r="E7">
+      <c r="E11">
         <v>0.04892056143049755</v>
       </c>
-      <c r="F7">
+      <c r="F11">
         <v>0.8649257552483359</v>
       </c>
-      <c r="G7">
+      <c r="G11">
         <v>0.03544213755164115</v>
       </c>
-      <c r="H7">
+      <c r="H11">
         <v>0.7428571428571428</v>
       </c>
-      <c r="I7">
+      <c r="I11">
         <v>0.06388765649999396</v>
       </c>
-      <c r="J7">
+      <c r="J11">
         <v>0.9004251700680271</v>
       </c>
-      <c r="K7">
+      <c r="K11">
         <v>0.03084373687103363</v>
       </c>
-      <c r="L7">
+      <c r="L11">
         <v>0.6875</v>
       </c>
-      <c r="M7">
+      <c r="M11">
         <v>0.08060477716637406</v>
       </c>
-      <c r="N7">
+      <c r="N11">
         <v>0.7133333333333333</v>
       </c>
-      <c r="O7">
+      <c r="O11">
         <v>0.06871017708734384</v>
       </c>
-      <c r="P7">
+      <c r="P11">
         <v>0.1099854403337434</v>
       </c>
-      <c r="Q7">
+      <c r="Q11">
         <v>0.01528182621833185</v>
       </c>
-      <c r="R7">
+      <c r="R11">
         <v>0.8487255483106104</v>
       </c>
-      <c r="S7">
+      <c r="S11">
         <v>0.8172910647252214</v>
       </c>
-      <c r="T7">
+      <c r="T11">
         <v>0.1099657010921379</v>
       </c>
-      <c r="U7">
+      <c r="U11">
         <v>217</v>
       </c>
-      <c r="V7">
+      <c r="V11">
         <v>24</v>
       </c>
-      <c r="W7">
+      <c r="W11">
         <v>18</v>
       </c>
-      <c r="X7">
+      <c r="X11">
         <v>52</v>
       </c>
     </row>
@@ -1017,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1025,36 +1333,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1086,7 +1394,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1118,7 +1426,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1150,7 +1458,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1182,7 +1490,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1305,7 +1613,7 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="J9">
-        <v>0.0925464678750603</v>
+        <v>0.09254646787506028</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1337,7 +1645,7 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="J10">
-        <v>0.074570865662166</v>
+        <v>0.07457086566216599</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1369,12 +1677,12 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="J11">
-        <v>0.09239668036191985</v>
+        <v>0.09239668036191986</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -1406,7 +1714,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -1438,7 +1746,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -1470,7 +1778,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>4</v>
@@ -1502,7 +1810,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1534,7 +1842,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1566,7 +1874,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -1598,7 +1906,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B19">
         <v>3</v>
@@ -1630,7 +1938,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1662,7 +1970,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -1694,7 +2002,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1726,7 +2034,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -1758,7 +2066,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -1790,7 +2098,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -1822,7 +2130,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B26">
         <v>5</v>
@@ -1854,7 +2162,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -1886,7 +2194,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -1918,7 +2226,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -1950,7 +2258,7 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -1982,7 +2290,7 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -2010,6 +2318,646 @@
       </c>
       <c r="J31">
         <v>0.09143827270433903</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>0.8746355685131195</v>
+      </c>
+      <c r="D32">
+        <v>0.7694003825306345</v>
+      </c>
+      <c r="E32">
+        <v>0.873015873015873</v>
+      </c>
+      <c r="F32">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G32">
+        <v>0.9183673469387755</v>
+      </c>
+      <c r="H32">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="I32">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="J32">
+        <v>0.09504853746134782</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>0.9300595238095237</v>
+      </c>
+      <c r="D33">
+        <v>0.8595943353306605</v>
+      </c>
+      <c r="E33">
+        <v>0.8870967741935484</v>
+      </c>
+      <c r="F33">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="G33">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H33">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="I33">
+        <v>0.72</v>
+      </c>
+      <c r="J33">
+        <v>0.07753912224224507</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34">
+        <v>0.8422619047619048</v>
+      </c>
+      <c r="D34">
+        <v>0.8232461079314983</v>
+      </c>
+      <c r="E34">
+        <v>0.9193548387096774</v>
+      </c>
+      <c r="F34">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G34">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="H34">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="I34">
+        <v>0.8</v>
+      </c>
+      <c r="J34">
+        <v>0.08065403117051272</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>0.9806547619047619</v>
+      </c>
+      <c r="D35">
+        <v>0.9411422902494331</v>
+      </c>
+      <c r="E35">
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="F35">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="G35">
+        <v>0.9375</v>
+      </c>
+      <c r="H35">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="I35">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="J35">
+        <v>0.06307854551233866</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36">
+        <v>0.8645833333333333</v>
+      </c>
+      <c r="D36">
+        <v>0.8236118024445549</v>
+      </c>
+      <c r="E36">
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="F36">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G36">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H36">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I36">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="J36">
+        <v>0.08430524597835072</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>0.8483965014577259</v>
+      </c>
+      <c r="D37">
+        <v>0.6698915119967752</v>
+      </c>
+      <c r="E37">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="F37">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G37">
+        <v>0.9387755102040817</v>
+      </c>
+      <c r="H37">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="I37">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="J37">
+        <v>0.1092063492063492</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>0.8660714285714285</v>
+      </c>
+      <c r="D38">
+        <v>0.7949857362299759</v>
+      </c>
+      <c r="E38">
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="F38">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G38">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H38">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I38">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="J38">
+        <v>0.07741935483870969</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39">
+        <v>3</v>
+      </c>
+      <c r="C39">
+        <v>0.8348214285714286</v>
+      </c>
+      <c r="D39">
+        <v>0.7138667783829074</v>
+      </c>
+      <c r="E39">
+        <v>0.9193548387096774</v>
+      </c>
+      <c r="F39">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G39">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="H39">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="I39">
+        <v>0.8</v>
+      </c>
+      <c r="J39">
+        <v>0.08516129032258064</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>0.9702380952380952</v>
+      </c>
+      <c r="D40">
+        <v>0.8633678351723464</v>
+      </c>
+      <c r="E40">
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="F40">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="G40">
+        <v>0.9375</v>
+      </c>
+      <c r="H40">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="I40">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="J40">
+        <v>0.06322580645161291</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41">
+        <v>5</v>
+      </c>
+      <c r="C41">
+        <v>0.8630952380952381</v>
+      </c>
+      <c r="D41">
+        <v>0.7114011660382629</v>
+      </c>
+      <c r="E41">
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="F41">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G41">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H41">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I41">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="J41">
+        <v>0.09290322580645162</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>0.8877551020408163</v>
+      </c>
+      <c r="D42">
+        <v>0.7774137527410796</v>
+      </c>
+      <c r="E42">
+        <v>0.8253968253968254</v>
+      </c>
+      <c r="F42">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G42">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="H42">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="I42">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="J42">
+        <v>0.1304551843967525</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43">
+        <v>0.9270833333333333</v>
+      </c>
+      <c r="D43">
+        <v>0.8494330680265361</v>
+      </c>
+      <c r="E43">
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="F43">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="G43">
+        <v>0.9375</v>
+      </c>
+      <c r="H43">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="I43">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="J43">
+        <v>0.1010118823942644</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
+      </c>
+      <c r="C44">
+        <v>0.8526785714285713</v>
+      </c>
+      <c r="D44">
+        <v>0.8281031893276791</v>
+      </c>
+      <c r="E44">
+        <v>0.8870967741935484</v>
+      </c>
+      <c r="F44">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G44">
+        <v>0.9375</v>
+      </c>
+      <c r="H44">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="I44">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="J44">
+        <v>0.09796452721310855</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45">
+        <v>4</v>
+      </c>
+      <c r="C45">
+        <v>0.9657738095238095</v>
+      </c>
+      <c r="D45">
+        <v>0.8894927336656659</v>
+      </c>
+      <c r="E45">
+        <v>0.9193548387096774</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H45">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="I45">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="J45">
+        <v>0.09920044515094774</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46">
+        <v>5</v>
+      </c>
+      <c r="C46">
+        <v>0.8794642857142857</v>
+      </c>
+      <c r="D46">
+        <v>0.8204029086382026</v>
+      </c>
+      <c r="E46">
+        <v>0.8870967741935484</v>
+      </c>
+      <c r="F46">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G46">
+        <v>0.9375</v>
+      </c>
+      <c r="H46">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="I46">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="J46">
+        <v>0.1033189092393783</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>0.9037900874635568</v>
+      </c>
+      <c r="D47">
+        <v>0.7812087319627974</v>
+      </c>
+      <c r="E47">
+        <v>0.873015873015873</v>
+      </c>
+      <c r="F47">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="G47">
+        <v>0.9387755102040817</v>
+      </c>
+      <c r="H47">
+        <v>0.75</v>
+      </c>
+      <c r="I47">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="J47">
+        <v>0.09674954929372057</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48">
+        <v>0.9449404761904763</v>
+      </c>
+      <c r="D48">
+        <v>0.8793749278549641</v>
+      </c>
+      <c r="E48">
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="F48">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G48">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H48">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I48">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="J48">
+        <v>0.07754859258198164</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="D49">
+        <v>0.8226889898433589</v>
+      </c>
+      <c r="E49">
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="F49">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G49">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H49">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I49">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="J49">
+        <v>0.08641393244141569</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50">
+        <v>0.9821428571428571</v>
+      </c>
+      <c r="D50">
+        <v>0.9444102641056422</v>
+      </c>
+      <c r="E50">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="F50">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="G50">
+        <v>0.9375</v>
+      </c>
+      <c r="H50">
+        <v>0.8125</v>
+      </c>
+      <c r="I50">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J50">
+        <v>0.06857244761330701</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51">
+        <v>0.9092261904761905</v>
+      </c>
+      <c r="D51">
+        <v>0.8476117265087852</v>
+      </c>
+      <c r="E51">
+        <v>0.8870967741935484</v>
+      </c>
+      <c r="F51">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="G51">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="H51">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="I51">
+        <v>0.72</v>
+      </c>
+      <c r="J51">
+        <v>0.08738316123455137</v>
       </c>
     </row>
   </sheetData>
